--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -53,12 +53,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -67,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,19 +152,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,13 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -796,14 +787,14 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>19.9</v>
+      <c r="D4" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n">
@@ -818,20 +809,20 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="12" t="n">
-        <v>16</v>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>451.2</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0.1</v>
@@ -843,7 +834,7 @@
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -855,13 +846,13 @@
         <v>11</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -877,20 +868,20 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="11" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F5" s="11" t="n">
+      <c r="D5" s="9" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>20.5</v>
@@ -904,15 +895,15 @@
       <c r="L5" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>13.9</v>
+      <c r="M5" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>1.4</v>
@@ -921,28 +912,28 @@
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>90.5</v>
+        <v>0.5</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.2</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -960,14 +951,14 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>19.4</v>
+      <c r="D6" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.1</v>
@@ -979,38 +970,38 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>26.1</v>
+        <v>5.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R6" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1019,13 +1010,13 @@
         <v>2.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1041,29 +1032,29 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F7" s="11" t="n">
+        <v>255</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>41.2</v>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>24.4</v>
@@ -1071,44 +1062,44 @@
       <c r="M7" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="N7" s="12" t="n">
-        <v>67.09999999999999</v>
+      <c r="N7" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>20</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.2</v>
+        <v>1.7</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X7" s="12" t="n">
-        <v>81.3</v>
+        <v>7</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1124,18 +1115,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G8" s="11" t="n">
+      <c r="E8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n"/>
@@ -1143,7 +1134,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1151,18 +1142,18 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="12" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>318.9</v>
+      <c r="M8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>29.8</v>
       </c>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1171,10 +1162,10 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>7.2</v>
+        <v>72</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.8</v>
@@ -1183,13 +1174,13 @@
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.2</v>
+        <v>10.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1205,17 +1196,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="13" t="n">
         <v>16.5</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>7.4</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>11.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1224,18 +1215,18 @@
         <v>61.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1128.9</v>
+        <v>8.9</v>
       </c>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="n">
-        <v>108.2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
@@ -1245,23 +1236,23 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>393.1</v>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n">
-        <v>95.5</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>87.2</v>
+        <v>80.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>94.8</v>
+        <v>994.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>429</v>
+        <v>929</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>1.6</v>
@@ -1282,14 +1273,14 @@
       <c r="C10" s="3" t="n">
         <v>156.3</v>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E10" s="11" t="n">
+      <c r="D10" s="9" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="E10" s="15" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>19.8</v>
+      <c r="F10" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>55</v>
@@ -1298,21 +1289,23 @@
         <v>61.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>74.3</v>
+        <v>29.3</v>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="n">
-        <v>118.6</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.8</v>
@@ -1327,25 +1320,25 @@
         <v>44.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>91.40000000000001</v>
+      <c r="V10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="X10" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1363,22 +1356,22 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>19.8</v>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
@@ -1390,16 +1383,16 @@
         <v>98.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="R11" s="12" t="n">
-        <v>81.7</v>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>89.5</v>
+        <v>9.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1.2</v>
@@ -1407,14 +1400,14 @@
       <c r="U11" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V11" s="12" t="n">
-        <v>18.6</v>
+      <c r="V11" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>20.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>1.1</v>
@@ -1434,20 +1427,20 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>41.8</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>10</v>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
@@ -1457,32 +1450,32 @@
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M12" s="12" t="n">
-        <v>78.90000000000001</v>
+      <c r="M12" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="12" t="n">
-        <v>17.9</v>
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>14.9</v>
+        <v>0.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>858.9</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.2</v>
@@ -1491,13 +1484,13 @@
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>93.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1513,16 +1506,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>19.8</v>
+      <c r="F13" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>13</v>
@@ -1531,34 +1524,34 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.5</v>
+        <v>10.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>23.8</v>
+        <v>20.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
@@ -1576,10 +1569,10 @@
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1596,16 +1589,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
-        <v>24.6</v>
+      <c r="D14" s="9" t="n">
+        <v>54.6</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="F14" s="16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G14" s="16" t="n">
+      <c r="F14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1618,7 +1611,7 @@
         <v>2.8</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>12.5</v>
@@ -1627,11 +1620,11 @@
         <v>1.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>24.6</v>
@@ -1645,23 +1638,23 @@
       <c r="T14" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>20.6</v>
+      <c r="U14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1680,14 +1673,14 @@
       <c r="D15" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>19.1</v>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.1</v>
@@ -1696,10 +1689,10 @@
         <v>2.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>4.4</v>
@@ -1709,11 +1702,11 @@
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1722,10 +1715,10 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
@@ -1733,11 +1726,11 @@
       <c r="W15" s="3" t="n">
         <v>83.5</v>
       </c>
-      <c r="X15" s="12" t="n">
-        <v>88.59999999999999</v>
+      <c r="X15" s="8" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1756,41 +1749,41 @@
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="15" t="n">
         <v>26.7</v>
       </c>
-      <c r="E16" s="18" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F16" s="18" t="n">
+      <c r="E16" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>23.6</v>
+        <v>2.6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>481.9</v>
+        <v>8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>4.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>97.8</v>
+        <v>90</v>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
@@ -1800,10 +1793,10 @@
         <v>1.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
@@ -1812,10 +1805,10 @@
         <v>4094.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>41.1</v>
@@ -1837,14 +1830,14 @@
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="9" t="n">
         <v>172.1</v>
       </c>
-      <c r="E17" s="16" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>19.1</v>
+      <c r="E17" s="9" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>62</v>
@@ -1856,25 +1849,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>66.2</v>
+        <v>60</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
@@ -1883,28 +1879,28 @@
         <v>46.1</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="U17" s="12" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>20.1</v>
+        <v>2.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X17" s="12" t="n">
-        <v>190.9</v>
+        <v>1.8</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>100.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>81.7</v>
+        <v>8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1920,23 +1916,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>9.800000000000001</v>
+      <c r="E18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.7</v>
@@ -1946,13 +1942,13 @@
       </c>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>998.6</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0</v>
@@ -1960,26 +1956,26 @@
       <c r="Q18" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="R18" s="12" t="n">
-        <v>19</v>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>742</v>
+        <v>10</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>15.1</v>
+        <v>10</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>63.2</v>
@@ -2001,14 +1997,14 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>19.9</v>
+      <c r="D19" s="9" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>9.6</v>
@@ -2017,11 +2013,11 @@
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n"/>
-      <c r="M19" s="12" t="n">
-        <v>14.9</v>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
@@ -2035,10 +2031,10 @@
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
@@ -2050,10 +2046,10 @@
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>84.8</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2072,26 +2068,26 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>10.6</v>
+      <c r="D20" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
@@ -2100,16 +2096,16 @@
         <v>0.3</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>96.8</v>
+        <v>6</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>231.4</v>
@@ -2117,17 +2113,17 @@
       <c r="R20" s="3" t="n">
         <v>115.1</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>28.8</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V20" s="12" t="n">
-        <v>91.2</v>
+        <v>2</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>42.2</v>
@@ -2136,10 +2132,10 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2155,17 +2151,17 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="11" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>19.8</v>
+      <c r="D21" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n">
@@ -2175,52 +2171,52 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
+        <v>10</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2236,26 +2232,26 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>90.59999999999999</v>
+      <c r="E22" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>5.1</v>
@@ -2264,44 +2260,44 @@
         <v>16.5</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>16.3</v>
+        <v>0.3</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1188.8</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n"/>
       <c r="Q22" s="3" t="n">
-        <v>24.6</v>
+        <v>25.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>99.8</v>
+        <v>29</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>12.7</v>
+        <v>1.3</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>161.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2319,20 +2315,20 @@
       <c r="C23" s="3" t="n">
         <v>128.2</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="15" t="n">
         <v>25.8</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>12.7</v>
+      <c r="E23" s="15" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>10.7</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>61.4</v>
+        <v>1.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53.9</v>
+        <v>53</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>2.5</v>
@@ -2341,45 +2337,45 @@
         <v>3.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>43.2</v>
       </c>
       <c r="M23" s="3" t="n"/>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>115.6</v>
+        <v>53.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
+        <v>1.5</v>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n">
         <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>219.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.3</v>
+        <v>9.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>86.3</v>
+        <v>80</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>76.7</v>
@@ -2398,44 +2394,44 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="15" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>97.5</v>
+      <c r="E24" s="9" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="12" t="n">
-        <v>1.7</v>
+      <c r="L24" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="R24" s="12" t="n">
-        <v>18.3</v>
+        <v>2.3</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.9</v>
@@ -2446,20 +2442,20 @@
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="12" t="n">
-        <v>89.40000000000001</v>
+      <c r="V24" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X24" s="12" t="n">
-        <v>17.8</v>
+        <v>0</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2479,9 +2475,9 @@
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F25" s="16" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>1.3</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2491,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>22</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.1</v>
@@ -2503,22 +2499,22 @@
         <v>1.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="Q25" s="12" t="n">
-        <v>1156.1</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>1.2</v>
@@ -2527,16 +2523,18 @@
         <v>0.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X25" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="3" t="n">
         <v>95</v>
       </c>
@@ -2557,22 +2555,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>22.8</v>
+        <v>1.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>19.3</v>
+        <v>13.5</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n">
@@ -2588,38 +2586,38 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W26" s="12" t="n">
-        <v>15.3</v>
+        <v>10.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2647,10 +2645,10 @@
       </c>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>4.3</v>
@@ -2660,16 +2658,16 @@
         <v>15.8</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N27" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P27" s="12" t="n">
-        <v>12.8</v>
+        <v>20</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>18</v>
@@ -2678,13 +2676,13 @@
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>19</v>
@@ -2693,13 +2691,13 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>21.8</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2715,14 +2713,14 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>18.5</v>
+      <c r="E28" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2738,32 +2736,32 @@
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="12" t="n">
-        <v>19.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2772,10 +2770,10 @@
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>99.8</v>
+        <v>10</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.9</v>
@@ -2797,18 +2795,18 @@
       <c r="D29" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F29" s="16" t="n">
-        <v>81.7</v>
+      <c r="F29" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.6</v>
@@ -2823,40 +2821,40 @@
         <v>44.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>434.3</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>19</v>
+      <c r="R29" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W29" s="12" t="n">
-        <v>31</v>
+        <v>0.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.2</v>
+        <v>9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2875,20 +2873,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1116.8</v>
-      </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>18.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>8.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.8</v>
@@ -2898,40 +2898,40 @@
       </c>
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>199.8</v>
+        <v>90</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4213.8</v>
+        <v>1.3</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>21.8</v>
+        <v>1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>1.3</v>
@@ -2956,20 +2956,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="15" t="n">
         <v>14.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>3.9</v>
@@ -2978,48 +2980,48 @@
         <v>2.5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>20</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>74.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3" t="n"/>
       <c r="Q31" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>7058</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="W31" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>92.09999999999999</v>
+      <c r="W31" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3035,31 +3037,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144 1
-</t>
-        </is>
+      <c r="E32" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
@@ -3069,47 +3068,44 @@
         <v>14.9</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.2</v>
+        <v>12</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>180.9</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R32" s="12" t="n">
+      <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="V32" s="3" t="n"/>
-      <c r="W32" s="12" t="n">
-        <v>16.2</v>
+      <c r="W32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">0 0 0
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 13
-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3125,22 +3121,22 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>90.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="9" t="n">
         <v>81.33</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.3</v>
+      <c r="G33" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
@@ -3150,32 +3146,32 @@
         <v>39.1</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
@@ -3184,13 +3180,13 @@
         <v>6.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>89.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3206,17 +3202,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="12" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F34" s="16" t="n">
+      <c r="D34" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>81.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.4</v>
@@ -3226,36 +3222,36 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>14.2</v>
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n"/>
       <c r="P34" s="3" t="n">
-        <v>10.6</v>
+        <v>20</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n">
-        <v>17.3</v>
+        <v>10</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96.8</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>16.4</v>
+        <v>0.4</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>52.2</v>
@@ -3267,7 +3263,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3283,72 +3279,72 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>14.2</v>
+      <c r="E35" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>15.1</v>
+        <v>1</v>
       </c>
       <c r="M35" s="3" t="n"/>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q35" s="12" t="n">
-        <v>76.90000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>15.9</v>
+        <v>10</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="W35" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X35" s="12" t="n">
-        <v>86.59999999999999</v>
+      <c r="W35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>218.6</v>
+        <v>0.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3367,14 +3363,14 @@
       <c r="D36" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -3386,23 +3382,23 @@
         <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="12" t="n">
-        <v>66.40000000000001</v>
+      <c r="N36" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>28.9</v>
+        <v>3</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>1.4</v>
@@ -3411,10 +3407,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>10</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
+        <v>10.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3423,13 +3419,13 @@
         <v>2.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>20.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3445,45 +3441,50 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="18" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E37" s="18" t="n">
+      <c r="D37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>13.8</v>
       </c>
-      <c r="F37" s="18" t="n">
-        <v>19.5</v>
+      <c r="F37" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 0
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>13.3</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.1</v>
+        <v>0.7</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>987.8</v>
+        <v>20</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>89.90000000000001</v>
@@ -3499,7 +3500,7 @@
       </c>
       <c r="V37" s="3" t="n"/>
       <c r="W37" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>7.6</v>
@@ -3508,7 +3509,7 @@
         <v>42.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>13.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3524,53 +3525,53 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="9" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="16" t="n">
-        <v>92.2</v>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n">
-        <v>56.9</v>
+        <v>50.9</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L38" s="12" t="n">
-        <v>81.3</v>
+      <c r="L38" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>90</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q38" s="12" t="n">
-        <v>18</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>90</v>
@@ -3582,10 +3583,10 @@
         <v>126.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>185.9</v>
+        <v>5.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3603,72 +3604,72 @@
       <c r="C39" s="3" t="n">
         <v>44.3</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>18.4</v>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>13.7</v>
+      <c r="L39" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>15.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="P39" s="12" t="n">
-        <v>8.4</v>
+        <v>9</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="12" t="n">
-        <v>81</v>
+      <c r="V39" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3684,74 +3685,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E40" s="13" t="n">
         <v>11.1</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>18.5</v>
+      <c r="F40" s="13" t="n">
+        <v>23.5</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16.3</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>17.6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>41.3</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>92.2</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P40" s="3" t="n"/>
       <c r="Q40" s="3" t="n">
-        <v>24.8</v>
+        <v>29.8</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>85.8</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>62.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>116.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3767,19 +3768,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>408.8</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D41" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="E41" s="11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F41" s="11" t="n">
+      <c r="E41" s="13" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F41" s="13" t="n">
         <v>17.9</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>16.2</v>
+      <c r="G41" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>34.7</v>
@@ -3794,31 +3795,31 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>1.3</v>
+        <v>0</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
@@ -3830,13 +3831,13 @@
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39.8</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3852,23 +3853,23 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E42" s="13" t="n"/>
+        <v>60.9</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.1</v>
@@ -3877,34 +3878,34 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>12.3</v>
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>920</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25.2</v>
+        <v>20</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>49.8</v>
+        <v>99</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -3916,10 +3917,10 @@
         <v>0.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3935,79 +3936,82 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>1.7</v>
+        <v>5</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>0.5</v>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I43" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>90</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.8</v>
+        <v>20.8</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S43" s="12" t="n">
-        <v>61.8</v>
+      <c r="S43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>18.9</v>
+        <v>10</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>20.5</v>
+        <v>5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4023,76 +4027,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>1.7</v>
+        <v>3109.5</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416 1
+          <t xml:space="preserve">00000 0
 </t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>0.5</v>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 0
+</t>
+        </is>
       </c>
       <c r="I44" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>5002</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>12.2</v>
+        <v>0</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>10110110.1</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S44" s="12" t="n">
-        <v>11</v>
+        <v>20.8</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>150115100011.5</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V44" s="12" t="n">
-        <v>1989.8</v>
+        <v>0</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>59.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>2.2</v>
@@ -4111,43 +4118,43 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
-      </c>
-      <c r="D45" s="18" t="n">
+        <v>3109.5</v>
+      </c>
+      <c r="D45" s="15" t="n">
         <v>31.3</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="15" t="n">
         <v>53.4</v>
       </c>
-      <c r="F45" s="18" t="n">
-        <v>92.5</v>
+      <c r="F45" s="15" t="n">
+        <v>22.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>56.9</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>53.1</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>621.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>498</v>
+        <v>90</v>
       </c>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
@@ -4157,25 +4164,25 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2929.8</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>729.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>108.9</v>
+        <v>1208.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>328.8</v>
+        <v>300.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>2.2</v>
@@ -4196,16 +4203,16 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F46" s="11" t="n">
+      <c r="D46" s="15" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F46" s="15" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4220,47 +4227,47 @@
       <c r="K46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>11.1</v>
+      <c r="L46" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>13.1</v>
+        <v>0.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <v>4.4</v>
+        <v>9</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.3</v>
+        <v>1.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>8.9</v>
+        <v>50</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>208.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1226,7 +1226,7 @@
       <c r="J9" s="3" t="n">
         <v>1128.9</v>
       </c>
-      <c r="K9" s="3" t="n"/>
+      <c r="K9" s="13" t="n"/>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
@@ -1363,8 +1363,8 @@
       <c r="C11" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="16" t="n">
         <v>1.6</v>
       </c>
@@ -1380,7 +1380,7 @@
       <c r="J11" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="14" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n">
         <v>14.9</v>
@@ -1439,7 +1439,7 @@
       <c r="D12" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="E12" s="13" t="n"/>
+      <c r="E12" s="14" t="n"/>
       <c r="F12" s="16" t="n">
         <v>0</v>
       </c>
@@ -1453,7 +1453,7 @@
       <c r="J12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K12" s="3" t="n"/>
+      <c r="K12" s="14" t="n"/>
       <c r="L12" s="3" t="n">
         <v>14.5</v>
       </c>
@@ -1777,7 +1777,7 @@
       <c r="J16" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="18" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -1941,7 +1941,7 @@
       <c r="J18" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="11" t="n">
         <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="L19" s="3" t="n"/>
@@ -2093,7 +2093,7 @@
       <c r="J20" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2174,7 +2174,7 @@
       <c r="J21" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
@@ -2257,7 +2257,7 @@
       <c r="J22" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="L22" s="3" t="n">
@@ -2340,7 +2340,7 @@
       <c r="J23" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2877,7 +2877,7 @@
       <c r="C30" s="3" t="n">
         <v>1116.8</v>
       </c>
-      <c r="D30" s="14" t="n"/>
+      <c r="D30" s="13" t="n"/>
       <c r="E30" s="18" t="n">
         <v>14</v>
       </c>
@@ -2896,7 +2896,7 @@
       <c r="J30" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="13" t="n"/>
       <c r="L30" s="3" t="n">
         <v>13.7</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="J32" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="14" t="n"/>
       <c r="L32" s="3" t="n">
         <v>15</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -3527,7 +3527,7 @@
       <c r="D38" s="16" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="14" t="n"/>
+      <c r="E38" s="13" t="n"/>
       <c r="F38" s="16" t="n">
         <v>92.2</v>
       </c>
@@ -3857,7 +3857,7 @@
       <c r="D42" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="E42" s="13" t="n"/>
+      <c r="E42" s="14" t="n"/>
       <c r="F42" s="3" t="n">
         <v>18.7</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
